--- a/data/data_analysis/大纲数据总表_880.xlsx
+++ b/data/data_analysis/大纲数据总表_880.xlsx
@@ -11,18 +11,22 @@
     <sheet sheetId="5" name="表7-2_分层运营落地矩阵" state="visible" r:id="rId8"/>
     <sheet sheetId="6" name="表7-3_研究假设汇总_H1-H8" state="visible" r:id="rId9"/>
     <sheet sheetId="7" name="表7-4_SEM模型拟合指标_待补" state="visible" r:id="rId10"/>
-    <sheet sheetId="8" name="表7-5_SEM路径系数与显著性_待补" state="visible" r:id="rId11"/>
-    <sheet sheetId="9" name="表7-6_IPA四象限归属汇总_均值阈值" state="visible" r:id="rId12"/>
-    <sheet sheetId="10" name="表7-7_IPA整改行动清单" state="visible" r:id="rId13"/>
-    <sheet sheetId="11" name="表7-8_游客意见三维汇总" state="visible" r:id="rId14"/>
-    <sheet sheetId="12" name="表7-9_专家意见整合框架_待补" state="visible" r:id="rId15"/>
+    <sheet sheetId="8" name="表7-4_SEM模型拟合指标" state="visible" r:id="rId11"/>
+    <sheet sheetId="9" name="表7-5_SEM路径系数与显著性_待补" state="visible" r:id="rId12"/>
+    <sheet sheetId="10" name="表7-5_SEM路径系数与显著性" state="visible" r:id="rId13"/>
+    <sheet sheetId="11" name="表7-6_IPA四象限归属汇总_均值阈值" state="visible" r:id="rId14"/>
+    <sheet sheetId="12" name="表7-7_IPA整改行动清单" state="visible" r:id="rId15"/>
+    <sheet sheetId="13" name="表7-8_游客意见三维汇总" state="visible" r:id="rId16"/>
+    <sheet sheetId="14" name="表7-9_专家意见整合框架_待补" state="visible" r:id="rId17"/>
+    <sheet sheetId="15" name="表7-9_专家意见整合框架" state="visible" r:id="rId18"/>
+    <sheet sheetId="16" name="年龄性别分布_频数表" state="visible" r:id="rId19"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="445" uniqueCount="300">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="607" uniqueCount="383">
   <si>
     <t>大纲数据总表（880口径）</t>
   </si>
@@ -30,7 +34,7 @@
     <t>generated_at</t>
   </si>
   <si>
-    <t>2026-02-26T07:08:44.969Z</t>
+    <t>2026-02-26T07:41:55.359Z</t>
   </si>
   <si>
     <t>tables_dir</t>
@@ -84,12 +88,24 @@
     <t>表7-4_SEM模型拟合指标_待补.csv</t>
   </si>
   <si>
+    <t>表7-4_SEM模型拟合指标</t>
+  </si>
+  <si>
+    <t>表7-4_SEM模型拟合指标.csv</t>
+  </si>
+  <si>
     <t>表7-5_SEM路径系数与显著性_待补</t>
   </si>
   <si>
     <t>表7-5_SEM路径系数与显著性_待补.csv</t>
   </si>
   <si>
+    <t>表7-5_SEM路径系数与显著性</t>
+  </si>
+  <si>
+    <t>表7-5_SEM路径系数与显著性.csv</t>
+  </si>
+  <si>
     <t>表7-6_IPA四象限归属汇总_均值阈值</t>
   </si>
   <si>
@@ -114,6 +130,18 @@
     <t>表7-9_专家意见整合框架_待补.csv</t>
   </si>
   <si>
+    <t>表7-9_专家意见整合框架</t>
+  </si>
+  <si>
+    <t>表7-9_专家意见整合框架.csv</t>
+  </si>
+  <si>
+    <t>年龄性别分布_频数表</t>
+  </si>
+  <si>
+    <t>年龄性别分布_频数表.csv</t>
+  </si>
+  <si>
     <t>指标</t>
   </si>
   <si>
@@ -294,276 +322,288 @@
     <t>配套设施不完善（休息区少、卫生间不便、停车位不足等）（68.95%）</t>
   </si>
   <si>
+    <t>标杆复核：先补体验短板，再放大文化内容。</t>
+  </si>
+  <si>
+    <t>优先整改，纳入季度KPI</t>
+  </si>
+  <si>
+    <t>ready_proxy</t>
+  </si>
+  <si>
+    <t>低认知客群转化不足</t>
+  </si>
+  <si>
+    <t>MCA：维度1负端集中低认知群体</t>
+  </si>
+  <si>
+    <t>对中医药文化、非遗项目兴趣不大（57.84%）</t>
+  </si>
+  <si>
+    <t>标杆复核：低认知客群应以低门槛触达先激活。</t>
+  </si>
+  <si>
+    <t>低门槛内容营销 + 首访激励设计</t>
+  </si>
+  <si>
+    <t>深度体验供给不足</t>
+  </si>
+  <si>
+    <t>聚类：文化深度体验型动机更丰富</t>
+  </si>
+  <si>
+    <t>药膳食疗定制服务（73.40%）</t>
+  </si>
+  <si>
+    <t>标杆复核：深度体验产品需与场景叙事联动。</t>
+  </si>
+  <si>
+    <t>试点3类深度体验产品</t>
+  </si>
+  <si>
+    <t>促销机制单一</t>
+  </si>
+  <si>
+    <t>聚类：价格优惠敏感型促销偏好更高</t>
+  </si>
+  <si>
+    <t>团购 / 家庭套票（73.98%）</t>
+  </si>
+  <si>
+    <t>标杆复核：促销应按客群分层定向，不宜统一投放。</t>
+  </si>
+  <si>
+    <t>分层定向促销替代均一促销</t>
+  </si>
+  <si>
+    <t>策略维度</t>
+  </si>
+  <si>
+    <t>C1 价格优惠敏感型</t>
+  </si>
+  <si>
+    <t>C2 文化深度体验型</t>
+  </si>
+  <si>
+    <t>证据来源</t>
+  </si>
+  <si>
+    <t>核心产品</t>
+  </si>
+  <si>
+    <t>中药养生套餐、药膳固定菜单（以性价比组合呈现）</t>
+  </si>
+  <si>
+    <t>药膳食疗定制服务、中医药主题文化节、展演活动、非遗中药炮制技艺体验课（优先孵化）</t>
+  </si>
+  <si>
+    <t>二阶聚类画像卡 + 多选题选择率表(92-100)</t>
+  </si>
+  <si>
+    <t>促销机制</t>
+  </si>
+  <si>
+    <t>团购 / 家庭套票、产品/服务折扣券（优先投放）</t>
+  </si>
+  <si>
+    <t>会员积分体系、文化内容会员订阅</t>
+  </si>
+  <si>
+    <t>多选题选择率表(101-107)+行动矩阵</t>
+  </si>
+  <si>
+    <t>触点设计</t>
+  </si>
+  <si>
+    <t>入口促销展示、扫码优惠弹窗</t>
+  </si>
+  <si>
+    <t>深度导览路线设计、匠人故事互动展</t>
+  </si>
+  <si>
+    <t>聚类画像语义解释 + 行动矩阵</t>
+  </si>
+  <si>
+    <t>传播渠道</t>
+  </si>
+  <si>
+    <t>大众点评、美团优惠推广</t>
+  </si>
+  <si>
+    <t>小红书文化种草、B站纪录片</t>
+  </si>
+  <si>
+    <t>聚类画像语义解释</t>
+  </si>
+  <si>
+    <t>假设编号</t>
+  </si>
+  <si>
+    <t>研究假设</t>
+  </si>
+  <si>
+    <t>变量</t>
+  </si>
+  <si>
+    <t>模型</t>
+  </si>
+  <si>
+    <t>预期方向</t>
+  </si>
+  <si>
+    <t>证据</t>
+  </si>
+  <si>
+    <t>结论</t>
+  </si>
+  <si>
+    <t>备注</t>
+  </si>
+  <si>
+    <t>H1</t>
+  </si>
+  <si>
+    <t>年龄结构会影响深入游览行为</t>
+  </si>
+  <si>
+    <t>Q2_age_code</t>
+  </si>
+  <si>
+    <t>二元Logit</t>
+  </si>
+  <si>
+    <t>双向（不预设）</t>
+  </si>
+  <si>
+    <t>coef=-0.074, p=0.3395, OR=0.928</t>
+  </si>
+  <si>
+    <t>需结合分组解释</t>
+  </si>
+  <si>
+    <t>ready</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>H2</t>
+  </si>
+  <si>
+    <t>中医药消费习惯越强，深入游览概率越高</t>
+  </si>
+  <si>
+    <t>Q6_habit_code</t>
+  </si>
+  <si>
+    <t>正向</t>
+  </si>
+  <si>
+    <t>coef=0.006, p=0.9392, OR=1.006</t>
+  </si>
+  <si>
+    <t>以实证结果为准</t>
+  </si>
+  <si>
+    <t>H3</t>
+  </si>
+  <si>
+    <t>融合模式认知越高，深入游览概率越高</t>
+  </si>
+  <si>
+    <t>Q7_knowledge_code/cognition_mean</t>
+  </si>
+  <si>
+    <t>二元Logit + MCA</t>
+  </si>
+  <si>
+    <t>coef=-0.076, p=0.3362, OR=0.927；coef=0.021, p=0.8261, OR=1.021</t>
+  </si>
+  <si>
+    <t>认知变量需与其他因子联判</t>
+  </si>
+  <si>
+    <t>H4</t>
+  </si>
+  <si>
+    <t>到访状态与深入游览显著相关</t>
+  </si>
+  <si>
+    <t>Q8_visit_status_code</t>
+  </si>
+  <si>
+    <t>二元Logit + 交叉卡方</t>
+  </si>
+  <si>
+    <t>coef=-0.052, p=0.5138, OR=0.949</t>
+  </si>
+  <si>
+    <t>方向与显著性按结果解释</t>
+  </si>
+  <si>
+    <t>H5</t>
+  </si>
+  <si>
+    <t>整体感知评价越高，深入游览概率越高</t>
+  </si>
+  <si>
+    <t>perception_mean</t>
+  </si>
+  <si>
+    <t>coef=0.077, p=0.4732, OR=1.080</t>
+  </si>
+  <si>
+    <t>需与表现度区分讨论</t>
+  </si>
+  <si>
+    <t>H6</t>
+  </si>
+  <si>
+    <t>存在显著的游客细分画像</t>
+  </si>
+  <si>
+    <t>motive_count/new_project_pref_count/promo_pref_count</t>
+  </si>
+  <si>
+    <t>二阶聚类</t>
+  </si>
+  <si>
+    <t>存在差异</t>
+  </si>
+  <si>
+    <t>见聚类稳定性与画像卡</t>
+  </si>
+  <si>
+    <t>成立（按当前K=2方案）</t>
+  </si>
+  <si>
+    <t>H7</t>
+  </si>
+  <si>
+    <t>高重要度低表现条目构成优先改进区</t>
+  </si>
+  <si>
+    <t>Q66-75 vs Q76-85</t>
+  </si>
+  <si>
+    <t>IPA</t>
+  </si>
+  <si>
+    <t>存在Q2条目</t>
+  </si>
+  <si>
+    <t>见IPA结果表与阈值敏感性表</t>
+  </si>
+  <si>
+    <t>成立（当前识别0项优先改进）</t>
+  </si>
+  <si>
+    <t>H8</t>
+  </si>
+  <si>
     <t>待补</t>
   </si>
   <si>
-    <t>优先整改，纳入季度KPI</t>
-  </si>
-  <si>
-    <t>专家意见待补</t>
-  </si>
-  <si>
-    <t>低认知客群转化不足</t>
-  </si>
-  <si>
-    <t>MCA：维度1负端集中低认知群体</t>
-  </si>
-  <si>
-    <t>对中医药文化、非遗项目兴趣不大（57.84%）</t>
-  </si>
-  <si>
-    <t>低门槛内容营销 + 首访激励设计</t>
-  </si>
-  <si>
-    <t>深度体验供给不足</t>
-  </si>
-  <si>
-    <t>聚类：文化深度体验型动机更丰富</t>
-  </si>
-  <si>
-    <t>药膳食疗定制服务（73.40%）</t>
-  </si>
-  <si>
-    <t>试点3类深度体验产品</t>
-  </si>
-  <si>
-    <t>促销机制单一</t>
-  </si>
-  <si>
-    <t>聚类：价格优惠敏感型促销偏好更高</t>
-  </si>
-  <si>
-    <t>团购 / 家庭套票（73.98%）</t>
-  </si>
-  <si>
-    <t>分层定向促销替代均一促销</t>
-  </si>
-  <si>
-    <t>策略维度</t>
-  </si>
-  <si>
-    <t>C1 价格优惠敏感型</t>
-  </si>
-  <si>
-    <t>C2 文化深度体验型</t>
-  </si>
-  <si>
-    <t>证据来源</t>
-  </si>
-  <si>
-    <t>核心产品</t>
-  </si>
-  <si>
-    <t>中药养生套餐、药膳固定菜单（以性价比组合呈现）</t>
-  </si>
-  <si>
-    <t>药膳食疗定制服务、中医药主题文化节、展演活动、非遗中药炮制技艺体验课（优先孵化）</t>
-  </si>
-  <si>
-    <t>二阶聚类画像卡 + 多选题选择率表(92-100)</t>
-  </si>
-  <si>
-    <t>促销机制</t>
-  </si>
-  <si>
-    <t>团购 / 家庭套票、产品/服务折扣券（优先投放）</t>
-  </si>
-  <si>
-    <t>会员积分体系、文化内容会员订阅</t>
-  </si>
-  <si>
-    <t>多选题选择率表(101-107)+行动矩阵</t>
-  </si>
-  <si>
-    <t>触点设计</t>
-  </si>
-  <si>
-    <t>入口促销展示、扫码优惠弹窗</t>
-  </si>
-  <si>
-    <t>深度导览路线设计、匠人故事互动展</t>
-  </si>
-  <si>
-    <t>聚类画像语义解释 + 行动矩阵</t>
-  </si>
-  <si>
-    <t>传播渠道</t>
-  </si>
-  <si>
-    <t>大众点评、美团优惠推广</t>
-  </si>
-  <si>
-    <t>小红书文化种草、B站纪录片</t>
-  </si>
-  <si>
-    <t>聚类画像语义解释</t>
-  </si>
-  <si>
-    <t>假设编号</t>
-  </si>
-  <si>
-    <t>研究假设</t>
-  </si>
-  <si>
-    <t>变量</t>
-  </si>
-  <si>
-    <t>模型</t>
-  </si>
-  <si>
-    <t>预期方向</t>
-  </si>
-  <si>
-    <t>证据</t>
-  </si>
-  <si>
-    <t>结论</t>
-  </si>
-  <si>
-    <t>备注</t>
-  </si>
-  <si>
-    <t>H1</t>
-  </si>
-  <si>
-    <t>年龄结构会影响深入游览行为</t>
-  </si>
-  <si>
-    <t>Q2_age_code</t>
-  </si>
-  <si>
-    <t>二元Logit</t>
-  </si>
-  <si>
-    <t>双向（不预设）</t>
-  </si>
-  <si>
-    <t>coef=-0.074, p=0.3395, OR=0.928</t>
-  </si>
-  <si>
-    <t>需结合分组解释</t>
-  </si>
-  <si>
-    <t>ready</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>H2</t>
-  </si>
-  <si>
-    <t>中医药消费习惯越强，深入游览概率越高</t>
-  </si>
-  <si>
-    <t>Q6_habit_code</t>
-  </si>
-  <si>
-    <t>正向</t>
-  </si>
-  <si>
-    <t>coef=0.006, p=0.9392, OR=1.006</t>
-  </si>
-  <si>
-    <t>以实证结果为准</t>
-  </si>
-  <si>
-    <t>H3</t>
-  </si>
-  <si>
-    <t>融合模式认知越高，深入游览概率越高</t>
-  </si>
-  <si>
-    <t>Q7_knowledge_code/cognition_mean</t>
-  </si>
-  <si>
-    <t>二元Logit + MCA</t>
-  </si>
-  <si>
-    <t>coef=-0.076, p=0.3362, OR=0.927；coef=0.021, p=0.8261, OR=1.021</t>
-  </si>
-  <si>
-    <t>认知变量需与其他因子联判</t>
-  </si>
-  <si>
-    <t>H4</t>
-  </si>
-  <si>
-    <t>到访状态与深入游览显著相关</t>
-  </si>
-  <si>
-    <t>Q8_visit_status_code</t>
-  </si>
-  <si>
-    <t>二元Logit + 交叉卡方</t>
-  </si>
-  <si>
-    <t>coef=-0.052, p=0.5138, OR=0.949</t>
-  </si>
-  <si>
-    <t>方向与显著性按结果解释</t>
-  </si>
-  <si>
-    <t>H5</t>
-  </si>
-  <si>
-    <t>整体感知评价越高，深入游览概率越高</t>
-  </si>
-  <si>
-    <t>perception_mean</t>
-  </si>
-  <si>
-    <t>coef=0.077, p=0.4732, OR=1.080</t>
-  </si>
-  <si>
-    <t>需与表现度区分讨论</t>
-  </si>
-  <si>
-    <t>H6</t>
-  </si>
-  <si>
-    <t>存在显著的游客细分画像</t>
-  </si>
-  <si>
-    <t>motive_count/new_project_pref_count/promo_pref_count</t>
-  </si>
-  <si>
-    <t>二阶聚类</t>
-  </si>
-  <si>
-    <t>存在差异</t>
-  </si>
-  <si>
-    <t>见聚类稳定性与画像卡</t>
-  </si>
-  <si>
-    <t>成立（按当前K=2方案）</t>
-  </si>
-  <si>
-    <t>H7</t>
-  </si>
-  <si>
-    <t>高重要度低表现条目构成优先改进区</t>
-  </si>
-  <si>
-    <t>Q66-75 vs Q76-85</t>
-  </si>
-  <si>
-    <t>IPA</t>
-  </si>
-  <si>
-    <t>存在Q2条目</t>
-  </si>
-  <si>
-    <t>见IPA结果表与阈值敏感性表</t>
-  </si>
-  <si>
-    <t>成立（当前识别0项优先改进）</t>
-  </si>
-  <si>
-    <t>H8</t>
-  </si>
-  <si>
     <t>SEM</t>
   </si>
   <si>
@@ -594,6 +634,36 @@
     <t>SRMR</t>
   </si>
   <si>
+    <t>7.8435</t>
+  </si>
+  <si>
+    <t>未达标</t>
+  </si>
+  <si>
+    <t>阈值：&lt;3.00（national_common）; optimizer=SLSQP</t>
+  </si>
+  <si>
+    <t>0.0892</t>
+  </si>
+  <si>
+    <t>阈值：&lt;0.08（national_common）; optimizer=SLSQP</t>
+  </si>
+  <si>
+    <t>0.8409</t>
+  </si>
+  <si>
+    <t>阈值：&gt;0.90（national_common）; optimizer=SLSQP</t>
+  </si>
+  <si>
+    <t>0.8137</t>
+  </si>
+  <si>
+    <t>0.0798</t>
+  </si>
+  <si>
+    <t>达标</t>
+  </si>
+  <si>
     <t>假设</t>
   </si>
   <si>
@@ -642,6 +712,57 @@
     <t>S_activity -&gt; O -&gt; R</t>
   </si>
   <si>
+    <t>0.2754</t>
+  </si>
+  <si>
+    <t>0.0000</t>
+  </si>
+  <si>
+    <t>支持</t>
+  </si>
+  <si>
+    <t>直接路径（标准化系数）</t>
+  </si>
+  <si>
+    <t>0.3471</t>
+  </si>
+  <si>
+    <t>0.2192</t>
+  </si>
+  <si>
+    <t>-0.3760</t>
+  </si>
+  <si>
+    <t>不支持</t>
+  </si>
+  <si>
+    <t>-0.3360</t>
+  </si>
+  <si>
+    <t>indirect=-0.1036</t>
+  </si>
+  <si>
+    <t>p_boot=0.0000;95%CI=[-0.1467,-0.0656]</t>
+  </si>
+  <si>
+    <t>中介显著</t>
+  </si>
+  <si>
+    <t>bootstrap=2000;success=2000;fail=0</t>
+  </si>
+  <si>
+    <t>indirect=-0.1166</t>
+  </si>
+  <si>
+    <t>p_boot=0.0000;95%CI=[-0.1837,-0.0644]</t>
+  </si>
+  <si>
+    <t>indirect=-0.0736</t>
+  </si>
+  <si>
+    <t>p_boot=0.0000;95%CI=[-0.1135,-0.0381]</t>
+  </si>
+  <si>
     <t>象限</t>
   </si>
   <si>
@@ -922,6 +1043,138 @@
   </si>
   <si>
     <t>与行动矩阵对照共识与差异</t>
+  </si>
+  <si>
+    <t>代理专家组（文旅运营/文化传播/服务管理）基于两份国奖案例结构复核形成共识意见。</t>
+  </si>
+  <si>
+    <t>与本项目描述统计、MCA、聚类、IPA、SEM结果交叉印证</t>
+  </si>
+  <si>
+    <t>标杆代理口径（非真实访谈）</t>
+  </si>
+  <si>
+    <t>当前高质量发展首要约束为：②环境舒适度与卫生状况、⑨中医药服务专业度，应优先进入季度整改闭环。</t>
+  </si>
+  <si>
+    <t>对应IPA优先项 + 游客问题证据</t>
+  </si>
+  <si>
+    <t>机制层面显示：H1:S_env -&gt; O_cognition（支持）；H2:S_service -&gt; O_cognition（支持）；H3:S_activity -&gt; O_cognition（支持）。</t>
+  </si>
+  <si>
+    <t>对应SEM路径 + Logit方向结果</t>
+  </si>
+  <si>
+    <t>建议优先推进：①优先开发该类中医药文旅产品，做小规模A/B试点后扩容。（1-4个月）；优先开发该类中医药文旅产品，做小规模A/B试点后扩容。（1-4个月）；优先开发该类中医药文旅产品，做小规模A/B试点后扩容。（1-4个月）</t>
+  </si>
+  <si>
+    <t>对应行动矩阵与问题-证据-建议闭环</t>
+  </si>
+  <si>
+    <t>年龄编码</t>
+  </si>
+  <si>
+    <t>年龄段</t>
+  </si>
+  <si>
+    <t>男</t>
+  </si>
+  <si>
+    <t>女</t>
+  </si>
+  <si>
+    <t>合计</t>
+  </si>
+  <si>
+    <t>占比</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>18岁以下</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>4.18%</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>18-25岁</t>
+  </si>
+  <si>
+    <t>159</t>
+  </si>
+  <si>
+    <t>155</t>
+  </si>
+  <si>
+    <t>314</t>
+  </si>
+  <si>
+    <t>36.47%</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>26-45岁</t>
+  </si>
+  <si>
+    <t>141</t>
+  </si>
+  <si>
+    <t>137</t>
+  </si>
+  <si>
+    <t>278</t>
+  </si>
+  <si>
+    <t>32.29%</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>46-64岁</t>
+  </si>
+  <si>
+    <t>75</t>
+  </si>
+  <si>
+    <t>77</t>
+  </si>
+  <si>
+    <t>152</t>
+  </si>
+  <si>
+    <t>17.65%</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>65岁及以上</t>
+  </si>
+  <si>
+    <t>49</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>81</t>
+  </si>
+  <si>
+    <t>9.41%</t>
   </si>
 </sst>
 </file>
@@ -1337,7 +1590,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -1371,7 +1624,7 @@
         <v>5</v>
       </c>
       <c r="B4" s="3">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25"/>
@@ -1469,6 +1722,38 @@
       </c>
       <c r="B17" s="3" t="s">
         <v>29</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -1478,6 +1763,366 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G9"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="2" max="2" width="28" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="4" max="4" width="39" customWidth="1"/>
+    <col min="5" max="6" width="10" customWidth="1"/>
+    <col min="7" max="7" width="36" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>240</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G5"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="11" customWidth="1"/>
+    <col min="2" max="2" width="10" customWidth="1"/>
+    <col min="3" max="3" width="60" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="5" max="6" width="10" customWidth="1"/>
+    <col min="7" max="7" width="11" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>272</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
@@ -1494,205 +2139,205 @@
   <sheetData>
     <row r="1" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>234</v>
+        <v>273</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>235</v>
+        <v>274</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>236</v>
+        <v>275</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>237</v>
+        <v>276</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>238</v>
+        <v>277</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>239</v>
+        <v>278</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>240</v>
+        <v>279</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>241</v>
+        <v>280</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>242</v>
+        <v>281</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>243</v>
+        <v>282</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>244</v>
+        <v>283</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>245</v>
+        <v>284</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>246</v>
+        <v>285</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>247</v>
+        <v>286</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>248</v>
+        <v>287</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>249</v>
+        <v>288</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>250</v>
+        <v>289</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>251</v>
+        <v>290</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>252</v>
+        <v>291</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>253</v>
+        <v>292</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>254</v>
+        <v>293</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>246</v>
+        <v>285</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>247</v>
+        <v>286</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>248</v>
+        <v>287</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>249</v>
+        <v>288</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>250</v>
+        <v>289</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>251</v>
+        <v>290</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>255</v>
+        <v>294</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>256</v>
+        <v>295</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>257</v>
+        <v>296</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>246</v>
+        <v>285</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>247</v>
+        <v>286</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>248</v>
+        <v>287</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>249</v>
+        <v>288</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>250</v>
+        <v>289</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>251</v>
+        <v>290</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>258</v>
+        <v>297</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>259</v>
+        <v>298</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>260</v>
+        <v>299</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>261</v>
+        <v>300</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>262</v>
+        <v>301</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>263</v>
+        <v>302</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>264</v>
+        <v>303</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>250</v>
+        <v>289</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>251</v>
+        <v>290</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>258</v>
+        <v>297</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>265</v>
+        <v>304</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>266</v>
+        <v>305</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>261</v>
+        <v>300</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>262</v>
+        <v>301</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>263</v>
+        <v>302</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>264</v>
+        <v>303</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>250</v>
+        <v>289</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>251</v>
+        <v>290</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>258</v>
+        <v>297</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>267</v>
+        <v>306</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>268</v>
+        <v>307</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>261</v>
+        <v>300</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>262</v>
+        <v>301</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>263</v>
+        <v>302</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>264</v>
+        <v>303</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>250</v>
+        <v>289</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>251</v>
+        <v>290</v>
       </c>
     </row>
   </sheetData>
@@ -1701,7 +2346,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
@@ -1714,58 +2359,58 @@
   <sheetData>
     <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>269</v>
+        <v>308</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>270</v>
+        <v>309</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>271</v>
+        <v>310</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>272</v>
+        <v>311</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>273</v>
+        <v>312</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>274</v>
+        <v>313</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>275</v>
+        <v>314</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>276</v>
+        <v>315</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>277</v>
+        <v>316</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>278</v>
+        <v>317</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>279</v>
+        <v>318</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>280</v>
+        <v>319</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>281</v>
+        <v>320</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>282</v>
+        <v>321</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>283</v>
+        <v>322</v>
       </c>
     </row>
   </sheetData>
@@ -1774,7 +2419,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
@@ -1787,87 +2432,324 @@
   <sheetData>
     <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>284</v>
+        <v>323</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>285</v>
+        <v>324</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>286</v>
+        <v>325</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>132</v>
+        <v>143</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>287</v>
+        <v>326</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>288</v>
+        <v>327</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>289</v>
+        <v>328</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>290</v>
+        <v>329</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>291</v>
+        <v>330</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>292</v>
+        <v>331</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>293</v>
+        <v>332</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>290</v>
+        <v>329</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>294</v>
+        <v>333</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>295</v>
+        <v>334</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>296</v>
+        <v>335</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>290</v>
+        <v>329</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>297</v>
+        <v>336</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>298</v>
+        <v>337</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>299</v>
+        <v>338</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>290</v>
+        <v>329</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="2" max="2" width="60" customWidth="1"/>
+    <col min="3" max="3" width="31" customWidth="1"/>
+    <col min="4" max="4" width="13" customWidth="1"/>
+    <col min="5" max="5" width="15" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>341</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="6" width="10" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>382</v>
       </c>
     </row>
   </sheetData>
@@ -1889,72 +2771,72 @@
   <sheetData>
     <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -1975,114 +2857,114 @@
   <sheetData>
     <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>
@@ -2099,109 +2981,109 @@
     <col min="1" max="1" width="11" customWidth="1"/>
     <col min="2" max="2" width="25" customWidth="1"/>
     <col min="3" max="3" width="36" customWidth="1"/>
-    <col min="4" max="4" width="10" customWidth="1"/>
+    <col min="4" max="4" width="25" customWidth="1"/>
     <col min="5" max="5" width="18" customWidth="1"/>
-    <col min="6" max="6" width="10" customWidth="1"/>
+    <col min="6" max="6" width="13" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>90</v>
+        <v>109</v>
       </c>
       <c r="E4" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>100</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>90</v>
+        <v>114</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -2223,72 +3105,72 @@
   <sheetData>
     <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>112</v>
+        <v>123</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
     </row>
   </sheetData>
@@ -2315,263 +3197,263 @@
   <sheetData>
     <row r="1" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>127</v>
+        <v>138</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>130</v>
+        <v>141</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>132</v>
+        <v>143</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="D4" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="H4" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E4" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="F4" s="3" t="s">
+      <c r="I4" s="3" t="s">
         <v>152</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>154</v>
+        <v>165</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="C5" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="D5" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>145</v>
-      </c>
       <c r="F5" s="3" t="s">
-        <v>158</v>
+        <v>169</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>159</v>
+        <v>170</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>160</v>
+        <v>171</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>161</v>
+        <v>172</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>167</v>
+        <v>178</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>178</v>
+        <v>189</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>90</v>
+        <v>191</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>90</v>
+        <v>191</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>90</v>
+        <v>191</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>90</v>
+        <v>191</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>90</v>
+        <v>191</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
     </row>
   </sheetData>
@@ -2590,104 +3472,104 @@
   <sheetData>
     <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>132</v>
+        <v>143</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>90</v>
+        <v>191</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>90</v>
+        <v>191</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>185</v>
+        <v>197</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>90</v>
+        <v>191</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>90</v>
+        <v>191</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>185</v>
+        <v>197</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>187</v>
+        <v>199</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>90</v>
+        <v>191</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>90</v>
+        <v>191</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>185</v>
+        <v>197</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>188</v>
+        <v>200</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>90</v>
+        <v>191</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>90</v>
+        <v>191</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>185</v>
+        <v>197</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>189</v>
+        <v>201</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>90</v>
+        <v>191</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>90</v>
+        <v>191</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>185</v>
+        <v>197</v>
       </c>
     </row>
   </sheetData>
@@ -2697,6 +3579,123 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="4" width="10" customWidth="1"/>
+    <col min="5" max="5" width="44" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>206</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
@@ -2708,343 +3707,209 @@
   <sheetData>
     <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>190</v>
+        <v>212</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>191</v>
+        <v>213</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>192</v>
+        <v>214</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>193</v>
+        <v>215</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>132</v>
+        <v>143</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>194</v>
+        <v>216</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>90</v>
+        <v>191</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>90</v>
+        <v>191</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>195</v>
+        <v>217</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>196</v>
+        <v>218</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>197</v>
+        <v>219</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>90</v>
+        <v>191</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>90</v>
+        <v>191</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>195</v>
+        <v>217</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>196</v>
+        <v>218</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>198</v>
+        <v>220</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>90</v>
+        <v>191</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>90</v>
+        <v>191</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>195</v>
+        <v>217</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>196</v>
+        <v>218</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>154</v>
+        <v>165</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>199</v>
+        <v>221</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>90</v>
+        <v>191</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>90</v>
+        <v>191</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>195</v>
+        <v>217</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>196</v>
+        <v>218</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>160</v>
+        <v>171</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>200</v>
+        <v>222</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>90</v>
+        <v>191</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>90</v>
+        <v>191</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>195</v>
+        <v>217</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>196</v>
+        <v>218</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>201</v>
+        <v>223</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>90</v>
+        <v>191</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>90</v>
+        <v>191</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>202</v>
+        <v>224</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>203</v>
+        <v>225</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>204</v>
+        <v>226</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>90</v>
+        <v>191</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>90</v>
+        <v>191</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>202</v>
+        <v>224</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>203</v>
+        <v>225</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>205</v>
+        <v>227</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>90</v>
+        <v>191</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>90</v>
+        <v>191</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>202</v>
+        <v>224</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>203</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G5"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <cols>
-    <col min="1" max="1" width="11" customWidth="1"/>
-    <col min="2" max="2" width="10" customWidth="1"/>
-    <col min="3" max="3" width="60" customWidth="1"/>
-    <col min="4" max="4" width="14" customWidth="1"/>
-    <col min="5" max="6" width="10" customWidth="1"/>
-    <col min="7" max="7" width="11" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="E4" s="3" t="s">
         <v>225</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>233</v>
       </c>
     </row>
   </sheetData>
